--- a/Claude outputs/Katalog_malumotlari.xlsx
+++ b/Claude outputs/Katalog_malumotlari.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zavod haqida" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mahsulotlar'!$A$3:$Q$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mahsulotlar'!$A$3:$X$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,11 +19,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.0#"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.00#"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,8 +81,14 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -105,6 +113,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -134,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -160,6 +178,18 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -525,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q60"/>
+  <dimension ref="A1:X60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -545,6 +575,13 @@
     <col width="32" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="23" max="23"/>
+    <col width="40" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -557,7 +594,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sariq kataklarni to'ldiring. Kulrang kataklar tizimdan olingan (normadan) — tekshirib, xato bo'lsa tuzating. 4-qator — namuna (to'ldirish shakli).</t>
+          <t>Sariq — siz to'ldirasiz. Kulrang — tizimdan (normadan). Ko'k — zhbi5.ru saytidan olindi (seriya bo'yicha standart qiymatlar), tekshirib chiqing. Qizil — tekshirish kerak.</t>
         </is>
       </c>
     </row>
@@ -647,6 +684,41 @@
           <t>Izoh</t>
         </is>
       </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>Beton klassi (B)</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>Sovuqqa chidamlilik (F)</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Suv o'tkazmaslik (W)</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>Hajm saytda, m³</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Po'lat saytda, kg</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>Manba (zhbi5.ru)</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Tekshirish kerak</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -735,10 +807,18 @@
       </c>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
-      <c r="H5" s="8" t="n"/>
-      <c r="I5" s="8" t="n"/>
+      <c r="F5" s="15" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>400</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>430</v>
+      </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
           <t>М 200</t>
@@ -751,10 +831,45 @@
         <v>44.1</v>
       </c>
       <c r="M5" s="7" t="n"/>
-      <c r="N5" s="7" t="n"/>
-      <c r="O5" s="7" t="n"/>
+      <c r="N5" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407.1-157 вып.1</t>
+        </is>
+      </c>
+      <c r="O5" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные лотки и лежни на подстанциях / ОРУ (серия 3.407.1-157)</t>
+        </is>
+      </c>
       <c r="P5" s="7" t="n"/>
       <c r="Q5" s="7" t="n"/>
+      <c r="R5" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S5" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T5" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U5" s="17" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="V5" s="18" t="n">
+        <v>44</v>
+      </c>
+      <c r="W5" s="19" t="inlineStr">
+        <is>
+          <t>ЛЖ-16</t>
+        </is>
+      </c>
+      <c r="X5" s="20" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -774,10 +889,18 @@
       </c>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
+      <c r="F6" s="15" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>400</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>750</v>
+      </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
           <t>М 200</t>
@@ -790,10 +913,49 @@
         <v>49.8</v>
       </c>
       <c r="M6" s="7" t="n"/>
-      <c r="N6" s="7" t="n"/>
-      <c r="O6" s="7" t="n"/>
+      <c r="N6" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407.1-157 вып.1</t>
+        </is>
+      </c>
+      <c r="O6" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные лотки и лежни на подстанциях / ОРУ (серия 3.407.1-157)</t>
+        </is>
+      </c>
       <c r="P6" s="7" t="n"/>
       <c r="Q6" s="7" t="n"/>
+      <c r="R6" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S6" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T6" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U6" s="17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V6" s="18" t="n">
+        <v>73</v>
+      </c>
+      <c r="W6" s="19" t="inlineStr">
+        <is>
+          <t>ЛЖ-28</t>
+        </is>
+      </c>
+      <c r="X6" s="21" t="inlineStr">
+        <is>
+          <t>Normadagi armatura 49.8 kg, seriyada jami po'lat 73 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -813,10 +975,18 @@
       </c>
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="8" t="n"/>
+      <c r="F7" s="15" t="n">
+        <v>5970</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>1480</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>3600</v>
+      </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -829,10 +999,45 @@
         <v>166.9</v>
       </c>
       <c r="M7" s="7" t="n"/>
-      <c r="N7" s="7" t="n"/>
-      <c r="O7" s="7" t="n"/>
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.1</t>
+        </is>
+      </c>
+      <c r="O7" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные каналы: прокладка силовых и контрольных кабелей, тепловые сети (серия 3.006.1-2.87)</t>
+        </is>
+      </c>
       <c r="P7" s="7" t="n"/>
       <c r="Q7" s="7" t="n"/>
+      <c r="R7" s="16" t="inlineStr">
+        <is>
+          <t>B25</t>
+        </is>
+      </c>
+      <c r="S7" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T7" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U7" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V7" s="18" t="n">
+        <v>164.1</v>
+      </c>
+      <c r="W7" s="19" t="inlineStr">
+        <is>
+          <t>Л11-8</t>
+        </is>
+      </c>
+      <c r="X7" s="20" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -852,18 +1057,61 @@
       </c>
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
+      <c r="F8" s="15" t="n">
+        <v>720</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>1480</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>450</v>
+      </c>
       <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="9" t="n"/>
       <c r="L8" s="10" t="n"/>
       <c r="M8" s="7" t="n"/>
-      <c r="N8" s="7" t="n"/>
-      <c r="O8" s="7" t="n"/>
+      <c r="N8" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.1</t>
+        </is>
+      </c>
+      <c r="O8" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные каналы: прокладка силовых и контрольных кабелей, тепловые сети (серия 3.006.1-2.87)</t>
+        </is>
+      </c>
       <c r="P8" s="7" t="n"/>
       <c r="Q8" s="7" t="n"/>
+      <c r="R8" s="16" t="inlineStr">
+        <is>
+          <t>B25</t>
+        </is>
+      </c>
+      <c r="S8" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T8" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U8" s="17" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="V8" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="W8" s="19" t="inlineStr">
+        <is>
+          <t>Л11д-8</t>
+        </is>
+      </c>
+      <c r="X8" s="20" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -883,10 +1131,18 @@
       </c>
       <c r="D9" s="7" t="n"/>
       <c r="E9" s="7" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
+      <c r="F9" s="15" t="n">
+        <v>5970</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>1480</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>1010</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>4800</v>
+      </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
           <t>М 300</t>
@@ -899,10 +1155,49 @@
         <v>73.3</v>
       </c>
       <c r="M9" s="7" t="n"/>
-      <c r="N9" s="7" t="n"/>
-      <c r="O9" s="7" t="n"/>
+      <c r="N9" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.1</t>
+        </is>
+      </c>
+      <c r="O9" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные каналы: прокладка силовых и контрольных кабелей, тепловые сети (серия 3.006.1-2.87)</t>
+        </is>
+      </c>
       <c r="P9" s="7" t="n"/>
       <c r="Q9" s="7" t="n"/>
+      <c r="R9" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S9" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T9" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U9" s="17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V9" s="18" t="n">
+        <v>142.6</v>
+      </c>
+      <c r="W9" s="19" t="inlineStr">
+        <is>
+          <t>Л12-8</t>
+        </is>
+      </c>
+      <c r="X9" s="21" t="inlineStr">
+        <is>
+          <t>Normadagi armatura 73.3 kg, seriyada jami po'lat 142.6 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -922,10 +1217,18 @@
       </c>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
+      <c r="F10" s="15" t="n">
+        <v>5970</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>1480</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>6300</v>
+      </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -938,10 +1241,45 @@
         <v>216.2</v>
       </c>
       <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="n"/>
-      <c r="O10" s="7" t="n"/>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.1</t>
+        </is>
+      </c>
+      <c r="O10" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные каналы: прокладка силовых и контрольных кабелей, тепловые сети (серия 3.006.1-2.87)</t>
+        </is>
+      </c>
       <c r="P10" s="7" t="n"/>
       <c r="Q10" s="7" t="n"/>
+      <c r="R10" s="16" t="inlineStr">
+        <is>
+          <t>B25</t>
+        </is>
+      </c>
+      <c r="S10" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T10" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U10" s="17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V10" s="18" t="n">
+        <v>212.7</v>
+      </c>
+      <c r="W10" s="19" t="inlineStr">
+        <is>
+          <t>Л13-11</t>
+        </is>
+      </c>
+      <c r="X10" s="20" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -961,18 +1299,61 @@
       </c>
       <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
+      <c r="F11" s="15" t="n">
+        <v>720</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>1480</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>800</v>
+      </c>
       <c r="J11" s="5" t="inlineStr"/>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="10" t="n"/>
       <c r="M11" s="7" t="n"/>
-      <c r="N11" s="7" t="n"/>
-      <c r="O11" s="7" t="n"/>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.1</t>
+        </is>
+      </c>
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные каналы: прокладка силовых и контрольных кабелей, тепловые сети (серия 3.006.1-2.87)</t>
+        </is>
+      </c>
       <c r="P11" s="7" t="n"/>
       <c r="Q11" s="7" t="n"/>
+      <c r="R11" s="16" t="inlineStr">
+        <is>
+          <t>B25</t>
+        </is>
+      </c>
+      <c r="S11" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T11" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U11" s="17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="V11" s="18" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="W11" s="19" t="inlineStr">
+        <is>
+          <t>Л13д-11</t>
+        </is>
+      </c>
+      <c r="X11" s="20" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -992,10 +1373,18 @@
       </c>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
+      <c r="F12" s="15" t="n">
+        <v>5970</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>570</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>360</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>900</v>
+      </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
           <t>М 300</t>
@@ -1008,10 +1397,45 @@
         <v>16.4</v>
       </c>
       <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="n"/>
-      <c r="O12" s="7" t="n"/>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.1</t>
+        </is>
+      </c>
+      <c r="O12" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные каналы: прокладка силовых и контрольных кабелей, тепловые сети (серия 3.006.1-2.87)</t>
+        </is>
+      </c>
       <c r="P12" s="7" t="n"/>
       <c r="Q12" s="7" t="n"/>
+      <c r="R12" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S12" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T12" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U12" s="17" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="V12" s="18" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="W12" s="19" t="inlineStr">
+        <is>
+          <t>Л2-8</t>
+        </is>
+      </c>
+      <c r="X12" s="20" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1031,18 +1455,61 @@
       </c>
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="8" t="n"/>
+      <c r="F13" s="15" t="n">
+        <v>1990</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>160</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>280</v>
+      </c>
       <c r="J13" s="5" t="inlineStr"/>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="10" t="n"/>
       <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
-      <c r="O13" s="7" t="n"/>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407.1-157 вып.1</t>
+        </is>
+      </c>
+      <c r="O13" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные лотки и лежни на подстанциях / ОРУ (серия 3.407.1-157)</t>
+        </is>
+      </c>
       <c r="P13" s="7" t="n"/>
       <c r="Q13" s="7" t="n"/>
+      <c r="R13" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S13" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T13" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U13" s="17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V13" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" s="19" t="inlineStr">
+        <is>
+          <t>Л20.10</t>
+        </is>
+      </c>
+      <c r="X13" s="20" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1062,10 +1529,18 @@
       </c>
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n"/>
+      <c r="F14" s="15" t="n">
+        <v>1990</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>160</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>180</v>
+      </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -1078,10 +1553,45 @@
         <v>6.5</v>
       </c>
       <c r="M14" s="7" t="n"/>
-      <c r="N14" s="7" t="n"/>
-      <c r="O14" s="7" t="n"/>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407.1-157 вып.1</t>
+        </is>
+      </c>
+      <c r="O14" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные лотки и лежни на подстанциях / ОРУ (серия 3.407.1-157)</t>
+        </is>
+      </c>
       <c r="P14" s="7" t="n"/>
       <c r="Q14" s="7" t="n"/>
+      <c r="R14" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S14" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T14" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U14" s="17" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V14" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="W14" s="19" t="inlineStr">
+        <is>
+          <t>Л20.5</t>
+        </is>
+      </c>
+      <c r="X14" s="20" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1101,10 +1611,18 @@
       </c>
       <c r="D15" s="7" t="n"/>
       <c r="E15" s="7" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
+      <c r="F15" s="15" t="n">
+        <v>5970</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>780</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>680</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>2250</v>
+      </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -1117,10 +1635,45 @@
         <v>44</v>
       </c>
       <c r="M15" s="7" t="n"/>
-      <c r="N15" s="7" t="n"/>
-      <c r="O15" s="7" t="n"/>
+      <c r="N15" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.1</t>
+        </is>
+      </c>
+      <c r="O15" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные каналы: прокладка силовых и контрольных кабелей, тепловые сети (серия 3.006.1-2.87)</t>
+        </is>
+      </c>
       <c r="P15" s="7" t="n"/>
       <c r="Q15" s="7" t="n"/>
+      <c r="R15" s="16" t="inlineStr">
+        <is>
+          <t>B25</t>
+        </is>
+      </c>
+      <c r="S15" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T15" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U15" s="17" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="V15" s="18" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="W15" s="19" t="inlineStr">
+        <is>
+          <t>Л5-15</t>
+        </is>
+      </c>
+      <c r="X15" s="20" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1140,10 +1693,18 @@
       </c>
       <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
+      <c r="F16" s="15" t="n">
+        <v>5970</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>780</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>680</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>2250</v>
+      </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -1156,10 +1717,45 @@
         <v>40.1</v>
       </c>
       <c r="M16" s="7" t="n"/>
-      <c r="N16" s="7" t="n"/>
-      <c r="O16" s="7" t="n"/>
+      <c r="N16" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.1</t>
+        </is>
+      </c>
+      <c r="O16" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные каналы: прокладка силовых и контрольных кабелей, тепловые сети (серия 3.006.1-2.87)</t>
+        </is>
+      </c>
       <c r="P16" s="7" t="n"/>
       <c r="Q16" s="7" t="n"/>
+      <c r="R16" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S16" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T16" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U16" s="17" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="V16" s="18" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="W16" s="19" t="inlineStr">
+        <is>
+          <t>Л5-8</t>
+        </is>
+      </c>
+      <c r="X16" s="20" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1179,18 +1775,61 @@
       </c>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
+      <c r="F17" s="15" t="n">
+        <v>720</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>780</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>680</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>280</v>
+      </c>
       <c r="J17" s="5" t="inlineStr"/>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="10" t="n"/>
       <c r="M17" s="7" t="n"/>
-      <c r="N17" s="7" t="n"/>
-      <c r="O17" s="7" t="n"/>
+      <c r="N17" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.1</t>
+        </is>
+      </c>
+      <c r="O17" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные каналы: прокладка силовых и контрольных кабелей, тепловые сети (серия 3.006.1-2.87)</t>
+        </is>
+      </c>
       <c r="P17" s="7" t="n"/>
       <c r="Q17" s="7" t="n"/>
+      <c r="R17" s="16" t="inlineStr">
+        <is>
+          <t>B25</t>
+        </is>
+      </c>
+      <c r="S17" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T17" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U17" s="17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V17" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W17" s="19" t="inlineStr">
+        <is>
+          <t>Л5д-15</t>
+        </is>
+      </c>
+      <c r="X17" s="20" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1210,10 +1849,18 @@
       </c>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
+      <c r="F18" s="15" t="n">
+        <v>5970</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>1160</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>530</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>2250</v>
+      </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -1226,10 +1873,45 @@
         <v>72.7</v>
       </c>
       <c r="M18" s="7" t="n"/>
-      <c r="N18" s="7" t="n"/>
-      <c r="O18" s="7" t="n"/>
+      <c r="N18" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.1</t>
+        </is>
+      </c>
+      <c r="O18" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные каналы: прокладка силовых и контрольных кабелей, тепловые сети (серия 3.006.1-2.87)</t>
+        </is>
+      </c>
       <c r="P18" s="7" t="n"/>
       <c r="Q18" s="7" t="n"/>
+      <c r="R18" s="16" t="inlineStr">
+        <is>
+          <t>B25</t>
+        </is>
+      </c>
+      <c r="S18" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T18" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U18" s="17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V18" s="18" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="W18" s="19" t="inlineStr">
+        <is>
+          <t>Л6-8</t>
+        </is>
+      </c>
+      <c r="X18" s="20" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1249,18 +1931,61 @@
       </c>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
+      <c r="F19" s="15" t="n">
+        <v>720</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>1160</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>530</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>280</v>
+      </c>
       <c r="J19" s="5" t="inlineStr"/>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="10" t="n"/>
       <c r="M19" s="7" t="n"/>
-      <c r="N19" s="7" t="n"/>
-      <c r="O19" s="7" t="n"/>
+      <c r="N19" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.1</t>
+        </is>
+      </c>
+      <c r="O19" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные каналы: прокладка силовых и контрольных кабелей, тепловые сети (серия 3.006.1-2.87)</t>
+        </is>
+      </c>
       <c r="P19" s="7" t="n"/>
       <c r="Q19" s="7" t="n"/>
+      <c r="R19" s="16" t="inlineStr">
+        <is>
+          <t>B25</t>
+        </is>
+      </c>
+      <c r="S19" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T19" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U19" s="17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V19" s="18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W19" s="19" t="inlineStr">
+        <is>
+          <t>Л6д-8</t>
+        </is>
+      </c>
+      <c r="X19" s="20" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1280,10 +2005,18 @@
       </c>
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
+      <c r="F20" s="15" t="n">
+        <v>5970</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>1160</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>3900</v>
+      </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -1296,10 +2029,45 @@
         <v>90.8</v>
       </c>
       <c r="M20" s="7" t="n"/>
-      <c r="N20" s="7" t="n"/>
-      <c r="O20" s="7" t="n"/>
+      <c r="N20" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.1</t>
+        </is>
+      </c>
+      <c r="O20" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные каналы: прокладка силовых и контрольных кабелей, тепловые сети (серия 3.006.1-2.87)</t>
+        </is>
+      </c>
       <c r="P20" s="7" t="n"/>
       <c r="Q20" s="7" t="n"/>
+      <c r="R20" s="16" t="inlineStr">
+        <is>
+          <t>B25</t>
+        </is>
+      </c>
+      <c r="S20" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T20" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U20" s="17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V20" s="18" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="W20" s="19" t="inlineStr">
+        <is>
+          <t>Л8-11</t>
+        </is>
+      </c>
+      <c r="X20" s="20" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1319,10 +2087,18 @@
       </c>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
+      <c r="F21" s="15" t="n">
+        <v>5970</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>1160</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>3900</v>
+      </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
           <t>М 300</t>
@@ -1335,10 +2111,49 @@
         <v>90.8</v>
       </c>
       <c r="M21" s="7" t="n"/>
-      <c r="N21" s="7" t="n"/>
-      <c r="O21" s="7" t="n"/>
+      <c r="N21" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.1</t>
+        </is>
+      </c>
+      <c r="O21" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные каналы: прокладка силовых и контрольных кабелей, тепловые сети (серия 3.006.1-2.87)</t>
+        </is>
+      </c>
       <c r="P21" s="7" t="n"/>
       <c r="Q21" s="7" t="n"/>
+      <c r="R21" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S21" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T21" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U21" s="17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V21" s="18" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="W21" s="19" t="inlineStr">
+        <is>
+          <t>Л8-5</t>
+        </is>
+      </c>
+      <c r="X21" s="21" t="inlineStr">
+        <is>
+          <t>Normadagi armatura 90.8 kg, seriyada jami po'lat 57.7 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1358,10 +2173,18 @@
       </c>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
+      <c r="F22" s="15" t="n">
+        <v>5970</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>1160</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>3900</v>
+      </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
           <t>М 300</t>
@@ -1374,10 +2197,45 @@
         <v>90.8</v>
       </c>
       <c r="M22" s="7" t="n"/>
-      <c r="N22" s="7" t="n"/>
-      <c r="O22" s="7" t="n"/>
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.1</t>
+        </is>
+      </c>
+      <c r="O22" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные каналы: прокладка силовых и контрольных кабелей, тепловые сети (серия 3.006.1-2.87)</t>
+        </is>
+      </c>
       <c r="P22" s="7" t="n"/>
       <c r="Q22" s="7" t="n"/>
+      <c r="R22" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S22" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T22" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U22" s="17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V22" s="18" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="W22" s="19" t="inlineStr">
+        <is>
+          <t>Л8-8</t>
+        </is>
+      </c>
+      <c r="X22" s="20" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1397,18 +2255,61 @@
       </c>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
+      <c r="F23" s="15" t="n">
+        <v>720</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>1160</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>500</v>
+      </c>
       <c r="J23" s="5" t="inlineStr"/>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="10" t="n"/>
       <c r="M23" s="7" t="n"/>
-      <c r="N23" s="7" t="n"/>
-      <c r="O23" s="7" t="n"/>
+      <c r="N23" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.1</t>
+        </is>
+      </c>
+      <c r="O23" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные каналы: прокладка силовых и контрольных кабелей, тепловые сети (серия 3.006.1-2.87)</t>
+        </is>
+      </c>
       <c r="P23" s="7" t="n"/>
       <c r="Q23" s="7" t="n"/>
+      <c r="R23" s="16" t="inlineStr">
+        <is>
+          <t>B25</t>
+        </is>
+      </c>
+      <c r="S23" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T23" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U23" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V23" s="18" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W23" s="19" t="inlineStr">
+        <is>
+          <t>Л8д-11</t>
+        </is>
+      </c>
+      <c r="X23" s="20" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1428,10 +2329,18 @@
       </c>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
+      <c r="F24" s="15" t="n">
+        <v>5970</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>1160</v>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>1310</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>5100</v>
+      </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -1444,10 +2353,45 @@
         <v>98.59999999999999</v>
       </c>
       <c r="M24" s="7" t="n"/>
-      <c r="N24" s="7" t="n"/>
-      <c r="O24" s="7" t="n"/>
+      <c r="N24" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.1</t>
+        </is>
+      </c>
+      <c r="O24" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные каналы: прокладка силовых и контрольных кабелей, тепловые сети (серия 3.006.1-2.87)</t>
+        </is>
+      </c>
       <c r="P24" s="7" t="n"/>
       <c r="Q24" s="7" t="n"/>
+      <c r="R24" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S24" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T24" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U24" s="17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V24" s="18" t="n">
+        <v>97</v>
+      </c>
+      <c r="W24" s="19" t="inlineStr">
+        <is>
+          <t>Л9-5</t>
+        </is>
+      </c>
+      <c r="X24" s="20" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1467,10 +2411,18 @@
       </c>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
+      <c r="F25" s="15" t="n">
+        <v>1990</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>160</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>180</v>
+      </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
           <t>М 300</t>
@@ -1483,10 +2435,49 @@
         <v>8.300000000000001</v>
       </c>
       <c r="M25" s="7" t="n"/>
-      <c r="N25" s="7" t="n"/>
-      <c r="O25" s="7" t="n"/>
+      <c r="N25" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407.1-157 вып.1</t>
+        </is>
+      </c>
+      <c r="O25" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные лотки и лежни на подстанциях / ОРУ (серия 3.407.1-157)</t>
+        </is>
+      </c>
       <c r="P25" s="7" t="n"/>
       <c r="Q25" s="7" t="n"/>
+      <c r="R25" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S25" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T25" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U25" s="17" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V25" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="W25" s="19" t="inlineStr">
+        <is>
+          <t>Л20.5</t>
+        </is>
+      </c>
+      <c r="X25" s="21" t="inlineStr">
+        <is>
+          <t>Saytda faqat «Л20.5» bor — ЛК-20.5 bilan bir xilmi, tekshiring; Normadagi hajm 0.145 ≠ seriyada 0.07 m³; Normadagi armatura 8.3 kg, seriyada jami po'lat 6 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1526,6 +2517,17 @@
       <c r="O26" s="7" t="n"/>
       <c r="P26" s="7" t="n"/>
       <c r="Q26" s="7" t="n"/>
+      <c r="R26" s="20" t="n"/>
+      <c r="S26" s="20" t="n"/>
+      <c r="T26" s="20" t="n"/>
+      <c r="U26" s="20" t="n"/>
+      <c r="V26" s="20" t="n"/>
+      <c r="W26" s="20" t="n"/>
+      <c r="X26" s="22" t="inlineStr">
+        <is>
+          <t>zhbi5.ru da topilmadi — o'zingiz to'ldirasiz</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1565,6 +2567,17 @@
       <c r="O27" s="7" t="n"/>
       <c r="P27" s="7" t="n"/>
       <c r="Q27" s="7" t="n"/>
+      <c r="R27" s="20" t="n"/>
+      <c r="S27" s="20" t="n"/>
+      <c r="T27" s="20" t="n"/>
+      <c r="U27" s="20" t="n"/>
+      <c r="V27" s="20" t="n"/>
+      <c r="W27" s="20" t="n"/>
+      <c r="X27" s="22" t="inlineStr">
+        <is>
+          <t>zhbi5.ru da topilmadi — o'zingiz to'ldirasiz</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -1584,10 +2597,18 @@
       </c>
       <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
+      <c r="F28" s="15" t="n">
+        <v>995</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>495</v>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v>70</v>
+      </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -1600,10 +2621,45 @@
         <v>4.5</v>
       </c>
       <c r="M28" s="7" t="n"/>
-      <c r="N28" s="7" t="n"/>
-      <c r="O28" s="7" t="n"/>
+      <c r="N28" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407.1-157 вып.1</t>
+        </is>
+      </c>
+      <c r="O28" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные лотки и лежни на подстанциях / ОРУ (серия 3.407.1-157)</t>
+        </is>
+      </c>
       <c r="P28" s="7" t="n"/>
       <c r="Q28" s="7" t="n"/>
+      <c r="R28" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S28" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T28" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U28" s="17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V28" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="W28" s="19" t="inlineStr">
+        <is>
+          <t>П10.5</t>
+        </is>
+      </c>
+      <c r="X28" s="20" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1623,10 +2679,18 @@
       </c>
       <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
+      <c r="F29" s="15" t="n">
+        <v>740</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>1480</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>190</v>
+      </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -1639,10 +2703,45 @@
         <v>5.5</v>
       </c>
       <c r="M29" s="7" t="n"/>
-      <c r="N29" s="7" t="n"/>
-      <c r="O29" s="7" t="n"/>
+      <c r="N29" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.2</t>
+        </is>
+      </c>
+      <c r="O29" s="16" t="inlineStr">
+        <is>
+          <t>Перекрытие кабельных лотков (серия 3.006.1-2.87, вып.2)</t>
+        </is>
+      </c>
       <c r="P29" s="7" t="n"/>
       <c r="Q29" s="7" t="n"/>
+      <c r="R29" s="16" t="inlineStr">
+        <is>
+          <t>B25</t>
+        </is>
+      </c>
+      <c r="S29" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T29" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U29" s="17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V29" s="18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W29" s="19" t="inlineStr">
+        <is>
+          <t>П10д-3</t>
+        </is>
+      </c>
+      <c r="X29" s="20" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -1662,10 +2761,18 @@
       </c>
       <c r="D30" s="7" t="n"/>
       <c r="E30" s="7" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="n"/>
+      <c r="F30" s="15" t="n">
+        <v>740</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>780</v>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>100</v>
+      </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -1678,10 +2785,49 @@
         <v>2.5</v>
       </c>
       <c r="M30" s="7" t="n"/>
-      <c r="N30" s="7" t="n"/>
-      <c r="O30" s="7" t="n"/>
+      <c r="N30" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.2</t>
+        </is>
+      </c>
+      <c r="O30" s="16" t="inlineStr">
+        <is>
+          <t>Перекрытие кабельных лотков (серия 3.006.1-2.87, вып.2)</t>
+        </is>
+      </c>
       <c r="P30" s="7" t="n"/>
       <c r="Q30" s="7" t="n"/>
+      <c r="R30" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S30" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T30" s="16" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="U30" s="17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V30" s="18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W30" s="19" t="inlineStr">
+        <is>
+          <t>П5д-5</t>
+        </is>
+      </c>
+      <c r="X30" s="21" t="inlineStr">
+        <is>
+          <t>Normadagi armatura 2.5 kg, seriyada jami po'lat 1.9 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -1701,10 +2847,18 @@
       </c>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="n"/>
+      <c r="F31" s="15" t="n">
+        <v>740</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>1160</v>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>150</v>
+      </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -1717,10 +2871,49 @@
         <v>4.5</v>
       </c>
       <c r="M31" s="7" t="n"/>
-      <c r="N31" s="7" t="n"/>
-      <c r="O31" s="7" t="n"/>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.006.1-2.87 вып.2</t>
+        </is>
+      </c>
+      <c r="O31" s="16" t="inlineStr">
+        <is>
+          <t>Перекрытие кабельных лотков (серия 3.006.1-2.87, вып.2)</t>
+        </is>
+      </c>
       <c r="P31" s="7" t="n"/>
       <c r="Q31" s="7" t="n"/>
+      <c r="R31" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S31" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T31" s="16" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="U31" s="17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="V31" s="18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="W31" s="19" t="inlineStr">
+        <is>
+          <t>П7д-3</t>
+        </is>
+      </c>
+      <c r="X31" s="21" t="inlineStr">
+        <is>
+          <t>Normadagi armatura 4.5 kg, seriyada jami po'lat 3.9 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -1740,10 +2933,18 @@
       </c>
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="n"/>
+      <c r="F32" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G32" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>600</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>2800</v>
+      </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
           <t>М 300</t>
@@ -1756,10 +2957,49 @@
         <v>95.5</v>
       </c>
       <c r="M32" s="7" t="n"/>
-      <c r="N32" s="7" t="n"/>
-      <c r="O32" s="7" t="n"/>
+      <c r="N32" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-115 вып.5</t>
+        </is>
+      </c>
+      <c r="O32" s="16" t="inlineStr">
+        <is>
+          <t>Анкерное закрепление опор ВЛ в грунте (серия 3.407-115, вып.5)</t>
+        </is>
+      </c>
       <c r="P32" s="7" t="n"/>
       <c r="Q32" s="7" t="n"/>
+      <c r="R32" s="16" t="inlineStr">
+        <is>
+          <t>B22,5</t>
+        </is>
+      </c>
+      <c r="S32" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T32" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U32" s="17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V32" s="18" t="n">
+        <v>114</v>
+      </c>
+      <c r="W32" s="19" t="inlineStr">
+        <is>
+          <t>ПА3-1</t>
+        </is>
+      </c>
+      <c r="X32" s="21" t="inlineStr">
+        <is>
+          <t>Normadagi armatura 95.5 kg, seriyada jami po'lat 114 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -1779,10 +3019,18 @@
       </c>
       <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
+      <c r="F33" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G33" s="15" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>600</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>3700</v>
+      </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
           <t>М 300</t>
@@ -1795,10 +3043,45 @@
         <v>197</v>
       </c>
       <c r="M33" s="7" t="n"/>
-      <c r="N33" s="7" t="n"/>
-      <c r="O33" s="7" t="n"/>
+      <c r="N33" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-115 вып.5</t>
+        </is>
+      </c>
+      <c r="O33" s="16" t="inlineStr">
+        <is>
+          <t>Анкерное закрепление опор ВЛ в грунте (серия 3.407-115, вып.5)</t>
+        </is>
+      </c>
       <c r="P33" s="7" t="n"/>
       <c r="Q33" s="7" t="n"/>
+      <c r="R33" s="16" t="inlineStr">
+        <is>
+          <t>B22,5</t>
+        </is>
+      </c>
+      <c r="S33" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T33" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U33" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V33" s="18" t="n">
+        <v>198</v>
+      </c>
+      <c r="W33" s="19" t="inlineStr">
+        <is>
+          <t>ПА3-2</t>
+        </is>
+      </c>
+      <c r="X33" s="20" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -1818,10 +3101,18 @@
       </c>
       <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
-      <c r="F34" s="8" t="n"/>
-      <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="8" t="n"/>
+      <c r="F34" s="15" t="n">
+        <v>995</v>
+      </c>
+      <c r="G34" s="15" t="n">
+        <v>495</v>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>70</v>
+      </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
           <t>М 300</t>
@@ -1834,10 +3125,49 @@
         <v>1.7</v>
       </c>
       <c r="M34" s="7" t="n"/>
-      <c r="N34" s="7" t="n"/>
-      <c r="O34" s="7" t="n"/>
+      <c r="N34" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407.1-157 вып.1</t>
+        </is>
+      </c>
+      <c r="O34" s="16" t="inlineStr">
+        <is>
+          <t>Кабельные лотки и лежни на подстанциях / ОРУ (серия 3.407.1-157)</t>
+        </is>
+      </c>
       <c r="P34" s="7" t="n"/>
       <c r="Q34" s="7" t="n"/>
+      <c r="R34" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S34" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T34" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U34" s="17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V34" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="W34" s="19" t="inlineStr">
+        <is>
+          <t>П10.5</t>
+        </is>
+      </c>
+      <c r="X34" s="21" t="inlineStr">
+        <is>
+          <t>Saytda «П10.5» — ПЛ 10.5 bilan bir xil ma'lumot olindi, tekshiring; Normadagi hajm 0.034 ≠ seriyada 0.03 m³; Normadagi armatura 1.7 kg, seriyada jami po'lat 4 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -1857,10 +3187,18 @@
       </c>
       <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
-      <c r="F35" s="8" t="n"/>
-      <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="n"/>
-      <c r="I35" s="8" t="n"/>
+      <c r="F35" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G35" s="15" t="n">
+        <v>400</v>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>200</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>500</v>
+      </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
           <t>М 300</t>
@@ -1873,10 +3211,45 @@
         <v>64</v>
       </c>
       <c r="M35" s="7" t="n"/>
-      <c r="N35" s="7" t="n"/>
-      <c r="O35" s="7" t="n"/>
+      <c r="N35" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-115 вып.5</t>
+        </is>
+      </c>
+      <c r="O35" s="16" t="inlineStr">
+        <is>
+          <t>Закрепление опор ВЛ в грунте (серия 3.407-115, вып.5)</t>
+        </is>
+      </c>
       <c r="P35" s="7" t="n"/>
       <c r="Q35" s="7" t="n"/>
+      <c r="R35" s="16" t="inlineStr">
+        <is>
+          <t>B22,5</t>
+        </is>
+      </c>
+      <c r="S35" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T35" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U35" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V35" s="18" t="n">
+        <v>62</v>
+      </c>
+      <c r="W35" s="19" t="inlineStr">
+        <is>
+          <t>АР5</t>
+        </is>
+      </c>
+      <c r="X35" s="20" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -1896,10 +3269,18 @@
       </c>
       <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="8" t="n"/>
+      <c r="F36" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G36" s="15" t="n">
+        <v>400</v>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>200</v>
+      </c>
+      <c r="I36" s="15" t="n">
+        <v>500</v>
+      </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
           <t>М 300</t>
@@ -1912,10 +3293,45 @@
         <v>40</v>
       </c>
       <c r="M36" s="7" t="n"/>
-      <c r="N36" s="7" t="n"/>
-      <c r="O36" s="7" t="n"/>
+      <c r="N36" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-115 вып.5</t>
+        </is>
+      </c>
+      <c r="O36" s="16" t="inlineStr">
+        <is>
+          <t>Закрепление опор ВЛ в грунте (серия 3.407-115, вып.5)</t>
+        </is>
+      </c>
       <c r="P36" s="7" t="n"/>
       <c r="Q36" s="7" t="n"/>
+      <c r="R36" s="16" t="inlineStr">
+        <is>
+          <t>B22,5</t>
+        </is>
+      </c>
+      <c r="S36" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T36" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U36" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V36" s="18" t="n">
+        <v>38</v>
+      </c>
+      <c r="W36" s="19" t="inlineStr">
+        <is>
+          <t>Р1-А</t>
+        </is>
+      </c>
+      <c r="X36" s="20" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -1935,10 +3351,18 @@
       </c>
       <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="n"/>
+      <c r="F37" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="G37" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>5200</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>800</v>
+      </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
           <t>М 200</t>
@@ -1951,10 +3375,45 @@
         <v>54.46</v>
       </c>
       <c r="M37" s="7" t="n"/>
-      <c r="N37" s="7" t="n"/>
-      <c r="O37" s="7" t="n"/>
+      <c r="N37" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-102 вып.1</t>
+        </is>
+      </c>
+      <c r="O37" s="16" t="inlineStr">
+        <is>
+          <t>Стойки под оборудование ОРУ подстанций (серия 3.407-102)</t>
+        </is>
+      </c>
       <c r="P37" s="7" t="n"/>
       <c r="Q37" s="7" t="n"/>
+      <c r="R37" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S37" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T37" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U37" s="17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="V37" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="W37" s="19" t="inlineStr">
+        <is>
+          <t>УСО-1А</t>
+        </is>
+      </c>
+      <c r="X37" s="20" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -1974,10 +3433,18 @@
       </c>
       <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
-      <c r="F38" s="8" t="n"/>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="8" t="n"/>
+      <c r="F38" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="G38" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>4400</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>700</v>
+      </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
           <t>М 200</t>
@@ -1990,10 +3457,49 @@
         <v>39.46</v>
       </c>
       <c r="M38" s="7" t="n"/>
-      <c r="N38" s="7" t="n"/>
-      <c r="O38" s="7" t="n"/>
+      <c r="N38" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-102 вып.1</t>
+        </is>
+      </c>
+      <c r="O38" s="16" t="inlineStr">
+        <is>
+          <t>Стойки под оборудование ОРУ подстанций (серия 3.407-102)</t>
+        </is>
+      </c>
       <c r="P38" s="7" t="n"/>
       <c r="Q38" s="7" t="n"/>
+      <c r="R38" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S38" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T38" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U38" s="17" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="V38" s="18" t="n">
+        <v>47</v>
+      </c>
+      <c r="W38" s="19" t="inlineStr">
+        <is>
+          <t>УСО-2А</t>
+        </is>
+      </c>
+      <c r="X38" s="21" t="inlineStr">
+        <is>
+          <t>Normadagi armatura 39.46 kg, seriyada jami po'lat 47 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -2013,10 +3519,18 @@
       </c>
       <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
-      <c r="F39" s="8" t="n"/>
-      <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="n"/>
-      <c r="I39" s="8" t="n"/>
+      <c r="F39" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="G39" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>600</v>
+      </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
           <t>М 300</t>
@@ -2029,10 +3543,49 @@
         <v>32</v>
       </c>
       <c r="M39" s="7" t="n"/>
-      <c r="N39" s="7" t="n"/>
-      <c r="O39" s="7" t="n"/>
+      <c r="N39" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-102 вып.1</t>
+        </is>
+      </c>
+      <c r="O39" s="16" t="inlineStr">
+        <is>
+          <t>Стойки под оборудование ОРУ подстанций (серия 3.407-102)</t>
+        </is>
+      </c>
       <c r="P39" s="7" t="n"/>
       <c r="Q39" s="7" t="n"/>
+      <c r="R39" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S39" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T39" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U39" s="17" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V39" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="W39" s="19" t="inlineStr">
+        <is>
+          <t>УСО-3А</t>
+        </is>
+      </c>
+      <c r="X39" s="21" t="inlineStr">
+        <is>
+          <t>Normadagi armatura 32 kg, seriyada jami po'lat 40 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -2052,10 +3605,18 @@
       </c>
       <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="8" t="n"/>
+      <c r="F40" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="G40" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>500</v>
+      </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
           <t>М 300</t>
@@ -2068,10 +3629,49 @@
         <v>27.2</v>
       </c>
       <c r="M40" s="7" t="n"/>
-      <c r="N40" s="7" t="n"/>
-      <c r="O40" s="7" t="n"/>
+      <c r="N40" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-102 вып.1</t>
+        </is>
+      </c>
+      <c r="O40" s="16" t="inlineStr">
+        <is>
+          <t>Стойки под оборудование ОРУ подстанций (серия 3.407-102)</t>
+        </is>
+      </c>
       <c r="P40" s="7" t="n"/>
       <c r="Q40" s="7" t="n"/>
+      <c r="R40" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S40" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T40" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U40" s="17" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="V40" s="18" t="n">
+        <v>35</v>
+      </c>
+      <c r="W40" s="19" t="inlineStr">
+        <is>
+          <t>УСО-4А</t>
+        </is>
+      </c>
+      <c r="X40" s="21" t="inlineStr">
+        <is>
+          <t>Normadagi armatura 27.2 kg, seriyada jami po'lat 35 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -2091,10 +3691,18 @@
       </c>
       <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
-      <c r="F41" s="8" t="n"/>
-      <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="8" t="n"/>
+      <c r="F41" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="G41" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>400</v>
+      </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
           <t>М 200</t>
@@ -2107,10 +3715,49 @@
         <v>19.92</v>
       </c>
       <c r="M41" s="7" t="n"/>
-      <c r="N41" s="7" t="n"/>
-      <c r="O41" s="7" t="n"/>
+      <c r="N41" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-102 вып.1</t>
+        </is>
+      </c>
+      <c r="O41" s="16" t="inlineStr">
+        <is>
+          <t>Стойки под оборудование ОРУ подстанций (серия 3.407-102)</t>
+        </is>
+      </c>
       <c r="P41" s="7" t="n"/>
       <c r="Q41" s="7" t="n"/>
+      <c r="R41" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S41" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T41" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U41" s="17" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="V41" s="18" t="n">
+        <v>27</v>
+      </c>
+      <c r="W41" s="19" t="inlineStr">
+        <is>
+          <t>УСО-5А</t>
+        </is>
+      </c>
+      <c r="X41" s="21" t="inlineStr">
+        <is>
+          <t>Normadagi armatura 19.92 kg, seriyada jami po'lat 27 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -2130,10 +3777,18 @@
       </c>
       <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
-      <c r="F42" s="8" t="n"/>
-      <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="8" t="n"/>
+      <c r="F42" s="15" t="n">
+        <v>800</v>
+      </c>
+      <c r="G42" s="15" t="n">
+        <v>800</v>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>400</v>
+      </c>
+      <c r="I42" s="15" t="n">
+        <v>300</v>
+      </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
           <t>М 200</t>
@@ -2146,10 +3801,45 @@
         <v>12</v>
       </c>
       <c r="M42" s="7" t="n"/>
-      <c r="N42" s="7" t="n"/>
-      <c r="O42" s="7" t="n"/>
+      <c r="N42" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-102 вып.1</t>
+        </is>
+      </c>
+      <c r="O42" s="16" t="inlineStr">
+        <is>
+          <t>Подножник под стойки УСО на ОРУ (серия 3.407-102)</t>
+        </is>
+      </c>
       <c r="P42" s="7" t="n"/>
       <c r="Q42" s="7" t="n"/>
+      <c r="R42" s="16" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="S42" s="16" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="T42" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="U42" s="17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="V42" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="W42" s="19" t="inlineStr">
+        <is>
+          <t>УБ-1</t>
+        </is>
+      </c>
+      <c r="X42" s="20" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -2169,10 +3859,18 @@
       </c>
       <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
-      <c r="F43" s="8" t="n"/>
-      <c r="G43" s="8" t="n"/>
-      <c r="H43" s="8" t="n"/>
-      <c r="I43" s="8" t="n"/>
+      <c r="F43" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G43" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H43" s="15" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I43" s="15" t="n">
+        <v>2400</v>
+      </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -2185,10 +3883,49 @@
         <v>82</v>
       </c>
       <c r="M43" s="7" t="n"/>
-      <c r="N43" s="7" t="n"/>
-      <c r="O43" s="7" t="n"/>
+      <c r="N43" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-115 вып.2</t>
+        </is>
+      </c>
+      <c r="O43" s="16" t="inlineStr">
+        <is>
+          <t>Фундаменты под стальные опоры ВЛ 35–500 кВ (серия 3.407-115)</t>
+        </is>
+      </c>
       <c r="P43" s="7" t="n"/>
       <c r="Q43" s="7" t="n"/>
+      <c r="R43" s="16" t="inlineStr">
+        <is>
+          <t>B30</t>
+        </is>
+      </c>
+      <c r="S43" s="16" t="inlineStr">
+        <is>
+          <t>F300</t>
+        </is>
+      </c>
+      <c r="T43" s="16" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="U43" s="17" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="V43" s="18" t="n">
+        <v>102</v>
+      </c>
+      <c r="W43" s="19" t="inlineStr">
+        <is>
+          <t>Ф2-2</t>
+        </is>
+      </c>
+      <c r="X43" s="21" t="inlineStr">
+        <is>
+          <t>Normadagi armatura 82 kg, seriyada jami po'lat 102 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -2208,10 +3945,18 @@
       </c>
       <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
-      <c r="F44" s="8" t="n"/>
-      <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="8" t="n"/>
+      <c r="F44" s="15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G44" s="15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>3200</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>3000</v>
+      </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -2224,10 +3969,45 @@
         <v>285</v>
       </c>
       <c r="M44" s="7" t="n"/>
-      <c r="N44" s="7" t="n"/>
-      <c r="O44" s="7" t="n"/>
+      <c r="N44" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-115 вып.2</t>
+        </is>
+      </c>
+      <c r="O44" s="16" t="inlineStr">
+        <is>
+          <t>Фундаменты под стальные опоры ВЛ 35–500 кВ (серия 3.407-115)</t>
+        </is>
+      </c>
       <c r="P44" s="7" t="n"/>
       <c r="Q44" s="7" t="n"/>
+      <c r="R44" s="16" t="inlineStr">
+        <is>
+          <t>B30</t>
+        </is>
+      </c>
+      <c r="S44" s="16" t="inlineStr">
+        <is>
+          <t>F300</t>
+        </is>
+      </c>
+      <c r="T44" s="16" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="U44" s="17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V44" s="18" t="n">
+        <v>311</v>
+      </c>
+      <c r="W44" s="19" t="inlineStr">
+        <is>
+          <t>Ф2-А</t>
+        </is>
+      </c>
+      <c r="X44" s="20" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -2247,10 +4027,18 @@
       </c>
       <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
-      <c r="F45" s="8" t="n"/>
-      <c r="G45" s="8" t="n"/>
-      <c r="H45" s="8" t="n"/>
-      <c r="I45" s="8" t="n"/>
+      <c r="F45" s="15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>2900</v>
+      </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
           <t>М 300</t>
@@ -2263,10 +4051,49 @@
         <v>69</v>
       </c>
       <c r="M45" s="7" t="n"/>
-      <c r="N45" s="7" t="n"/>
-      <c r="O45" s="7" t="n"/>
+      <c r="N45" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-115 вып.3</t>
+        </is>
+      </c>
+      <c r="O45" s="16" t="inlineStr">
+        <is>
+          <t>Фундаменты под стальные опоры ВЛ 35–500 кВ (серия 3.407-115)</t>
+        </is>
+      </c>
       <c r="P45" s="7" t="n"/>
       <c r="Q45" s="7" t="n"/>
+      <c r="R45" s="16" t="inlineStr">
+        <is>
+          <t>B22,5</t>
+        </is>
+      </c>
+      <c r="S45" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T45" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U45" s="17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V45" s="18" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="W45" s="19" t="inlineStr">
+        <is>
+          <t>Ф3-05</t>
+        </is>
+      </c>
+      <c r="X45" s="21" t="inlineStr">
+        <is>
+          <t>Normadagi armatura 69 kg, seriyada jami po'lat 102.2 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -2286,10 +4113,18 @@
       </c>
       <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
-      <c r="F46" s="8" t="n"/>
-      <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="n"/>
-      <c r="I46" s="8" t="n"/>
+      <c r="F46" s="15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G46" s="15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I46" s="15" t="n">
+        <v>2900</v>
+      </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -2302,10 +4137,49 @@
         <v>153</v>
       </c>
       <c r="M46" s="7" t="n"/>
-      <c r="N46" s="7" t="n"/>
-      <c r="O46" s="7" t="n"/>
+      <c r="N46" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-115 вып.2</t>
+        </is>
+      </c>
+      <c r="O46" s="16" t="inlineStr">
+        <is>
+          <t>Фундаменты под стальные опоры ВЛ 35–500 кВ (серия 3.407-115)</t>
+        </is>
+      </c>
       <c r="P46" s="7" t="n"/>
       <c r="Q46" s="7" t="n"/>
+      <c r="R46" s="16" t="inlineStr">
+        <is>
+          <t>B30</t>
+        </is>
+      </c>
+      <c r="S46" s="16" t="inlineStr">
+        <is>
+          <t>F300</t>
+        </is>
+      </c>
+      <c r="T46" s="16" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="U46" s="17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V46" s="18" t="n">
+        <v>133</v>
+      </c>
+      <c r="W46" s="19" t="inlineStr">
+        <is>
+          <t>Ф3-2</t>
+        </is>
+      </c>
+      <c r="X46" s="21" t="inlineStr">
+        <is>
+          <t>Normadagi armatura 153 kg, seriyada jami po'lat 133 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -2325,10 +4199,18 @@
       </c>
       <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
-      <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
+      <c r="F47" s="15" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G47" s="15" t="n">
+        <v>2100</v>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>3115</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>4300</v>
+      </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -2341,10 +4223,49 @@
         <v>253</v>
       </c>
       <c r="M47" s="7" t="n"/>
-      <c r="N47" s="7" t="n"/>
-      <c r="O47" s="7" t="n"/>
+      <c r="N47" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-115 вып.2</t>
+        </is>
+      </c>
+      <c r="O47" s="16" t="inlineStr">
+        <is>
+          <t>Фундаменты под стальные опоры ВЛ 35–500 кВ (серия 3.407-115)</t>
+        </is>
+      </c>
       <c r="P47" s="7" t="n"/>
       <c r="Q47" s="7" t="n"/>
+      <c r="R47" s="16" t="inlineStr">
+        <is>
+          <t>B30</t>
+        </is>
+      </c>
+      <c r="S47" s="16" t="inlineStr">
+        <is>
+          <t>F300</t>
+        </is>
+      </c>
+      <c r="T47" s="16" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="U47" s="17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V47" s="18" t="n">
+        <v>385</v>
+      </c>
+      <c r="W47" s="19" t="inlineStr">
+        <is>
+          <t>Ф3-Ам</t>
+        </is>
+      </c>
+      <c r="X47" s="21" t="inlineStr">
+        <is>
+          <t>Normadagi armatura 253 kg, seriyada jami po'lat 385 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -2384,6 +4305,17 @@
       <c r="O48" s="7" t="n"/>
       <c r="P48" s="7" t="n"/>
       <c r="Q48" s="7" t="n"/>
+      <c r="R48" s="20" t="n"/>
+      <c r="S48" s="20" t="n"/>
+      <c r="T48" s="20" t="n"/>
+      <c r="U48" s="20" t="n"/>
+      <c r="V48" s="20" t="n"/>
+      <c r="W48" s="20" t="n"/>
+      <c r="X48" s="22" t="inlineStr">
+        <is>
+          <t>zhbi5.ru da topilmadi — o'zingiz to'ldirasiz</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -2403,10 +4335,18 @@
       </c>
       <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
-      <c r="F49" s="8" t="n"/>
-      <c r="G49" s="8" t="n"/>
-      <c r="H49" s="8" t="n"/>
-      <c r="I49" s="8" t="n"/>
+      <c r="F49" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G49" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>3300</v>
+      </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
           <t>М 300</t>
@@ -2419,10 +4359,45 @@
         <v>137.7</v>
       </c>
       <c r="M49" s="7" t="n"/>
-      <c r="N49" s="7" t="n"/>
-      <c r="O49" s="7" t="n"/>
+      <c r="N49" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-115 вып.3</t>
+        </is>
+      </c>
+      <c r="O49" s="16" t="inlineStr">
+        <is>
+          <t>Фундаменты под стальные опоры ВЛ 35–500 кВ (серия 3.407-115)</t>
+        </is>
+      </c>
       <c r="P49" s="7" t="n"/>
       <c r="Q49" s="7" t="n"/>
+      <c r="R49" s="16" t="inlineStr">
+        <is>
+          <t>B22,5</t>
+        </is>
+      </c>
+      <c r="S49" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T49" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U49" s="17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V49" s="18" t="n">
+        <v>155</v>
+      </c>
+      <c r="W49" s="19" t="inlineStr">
+        <is>
+          <t>Ф4-05</t>
+        </is>
+      </c>
+      <c r="X49" s="20" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -2442,10 +4417,18 @@
       </c>
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="8" t="n"/>
-      <c r="G50" s="8" t="n"/>
-      <c r="H50" s="8" t="n"/>
-      <c r="I50" s="8" t="n"/>
+      <c r="F50" s="15" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G50" s="15" t="n">
+        <v>2100</v>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>3400</v>
+      </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -2458,10 +4441,45 @@
         <v>251</v>
       </c>
       <c r="M50" s="7" t="n"/>
-      <c r="N50" s="7" t="n"/>
-      <c r="O50" s="7" t="n"/>
+      <c r="N50" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-115 вып.2</t>
+        </is>
+      </c>
+      <c r="O50" s="16" t="inlineStr">
+        <is>
+          <t>Фундаменты под стальные опоры ВЛ 35–500 кВ (серия 3.407-115)</t>
+        </is>
+      </c>
       <c r="P50" s="7" t="n"/>
       <c r="Q50" s="7" t="n"/>
+      <c r="R50" s="16" t="inlineStr">
+        <is>
+          <t>B30</t>
+        </is>
+      </c>
+      <c r="S50" s="16" t="inlineStr">
+        <is>
+          <t>F300</t>
+        </is>
+      </c>
+      <c r="T50" s="16" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="U50" s="17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V50" s="18" t="n">
+        <v>278</v>
+      </c>
+      <c r="W50" s="19" t="inlineStr">
+        <is>
+          <t>Ф4-2</t>
+        </is>
+      </c>
+      <c r="X50" s="20" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -2481,10 +4499,18 @@
       </c>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="8" t="n"/>
-      <c r="G51" s="8" t="n"/>
-      <c r="H51" s="8" t="n"/>
-      <c r="I51" s="8" t="n"/>
+      <c r="F51" s="15" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G51" s="15" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>3115</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>5000</v>
+      </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -2497,10 +4523,49 @@
         <v>344</v>
       </c>
       <c r="M51" s="7" t="n"/>
-      <c r="N51" s="7" t="n"/>
-      <c r="O51" s="7" t="n"/>
+      <c r="N51" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-115 вып.2</t>
+        </is>
+      </c>
+      <c r="O51" s="16" t="inlineStr">
+        <is>
+          <t>Фундаменты под стальные опоры ВЛ 35–500 кВ (серия 3.407-115)</t>
+        </is>
+      </c>
       <c r="P51" s="7" t="n"/>
       <c r="Q51" s="7" t="n"/>
+      <c r="R51" s="16" t="inlineStr">
+        <is>
+          <t>B30</t>
+        </is>
+      </c>
+      <c r="S51" s="16" t="inlineStr">
+        <is>
+          <t>F300</t>
+        </is>
+      </c>
+      <c r="T51" s="16" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="U51" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V51" s="18" t="n">
+        <v>469</v>
+      </c>
+      <c r="W51" s="19" t="inlineStr">
+        <is>
+          <t>Ф4-Ам</t>
+        </is>
+      </c>
+      <c r="X51" s="21" t="inlineStr">
+        <is>
+          <t>Normadagi armatura 344 kg, seriyada jami po'lat 469 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -2540,6 +4605,17 @@
       <c r="O52" s="7" t="n"/>
       <c r="P52" s="7" t="n"/>
       <c r="Q52" s="7" t="n"/>
+      <c r="R52" s="20" t="n"/>
+      <c r="S52" s="20" t="n"/>
+      <c r="T52" s="20" t="n"/>
+      <c r="U52" s="20" t="n"/>
+      <c r="V52" s="20" t="n"/>
+      <c r="W52" s="20" t="n"/>
+      <c r="X52" s="22" t="inlineStr">
+        <is>
+          <t>zhbi5.ru da topilmadi — o'zingiz to'ldirasiz</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -2559,10 +4635,18 @@
       </c>
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
-      <c r="H53" s="8" t="n"/>
-      <c r="I53" s="8" t="n"/>
+      <c r="F53" s="15" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G53" s="15" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>3200</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>4480</v>
+      </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -2575,10 +4659,49 @@
         <v>323</v>
       </c>
       <c r="M53" s="7" t="n"/>
-      <c r="N53" s="7" t="n"/>
-      <c r="O53" s="7" t="n"/>
+      <c r="N53" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-115 вып.2</t>
+        </is>
+      </c>
+      <c r="O53" s="16" t="inlineStr">
+        <is>
+          <t>Фундаменты под стальные опоры ВЛ 35–500 кВ (серия 3.407-115)</t>
+        </is>
+      </c>
       <c r="P53" s="7" t="n"/>
       <c r="Q53" s="7" t="n"/>
+      <c r="R53" s="16" t="inlineStr">
+        <is>
+          <t>B30</t>
+        </is>
+      </c>
+      <c r="S53" s="16" t="inlineStr">
+        <is>
+          <t>F300</t>
+        </is>
+      </c>
+      <c r="T53" s="16" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="U53" s="17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V53" s="18" t="n">
+        <v>351</v>
+      </c>
+      <c r="W53" s="19" t="inlineStr">
+        <is>
+          <t>Ф5-2</t>
+        </is>
+      </c>
+      <c r="X53" s="21" t="inlineStr">
+        <is>
+          <t>Saytda Ф5-2 va Ф5-4 o'lchamlari bir xil berilgan — seriyadan tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -2598,10 +4721,18 @@
       </c>
       <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
-      <c r="F54" s="8" t="n"/>
-      <c r="G54" s="8" t="n"/>
-      <c r="H54" s="8" t="n"/>
-      <c r="I54" s="8" t="n"/>
+      <c r="F54" s="15" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G54" s="15" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>3200</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>4480</v>
+      </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -2614,10 +4745,45 @@
         <v>322</v>
       </c>
       <c r="M54" s="7" t="n"/>
-      <c r="N54" s="7" t="n"/>
-      <c r="O54" s="7" t="n"/>
+      <c r="N54" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-115 вып.2</t>
+        </is>
+      </c>
+      <c r="O54" s="16" t="inlineStr">
+        <is>
+          <t>Фундаменты под стальные опоры ВЛ 35–500 кВ (серия 3.407-115)</t>
+        </is>
+      </c>
       <c r="P54" s="7" t="n"/>
       <c r="Q54" s="7" t="n"/>
+      <c r="R54" s="16" t="inlineStr">
+        <is>
+          <t>B30</t>
+        </is>
+      </c>
+      <c r="S54" s="16" t="inlineStr">
+        <is>
+          <t>F300</t>
+        </is>
+      </c>
+      <c r="T54" s="16" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="U54" s="17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V54" s="18" t="n">
+        <v>375</v>
+      </c>
+      <c r="W54" s="19" t="inlineStr">
+        <is>
+          <t>Ф5-4</t>
+        </is>
+      </c>
+      <c r="X54" s="20" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -2637,10 +4803,18 @@
       </c>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="8" t="n"/>
-      <c r="G55" s="8" t="n"/>
-      <c r="H55" s="8" t="n"/>
-      <c r="I55" s="8" t="n"/>
+      <c r="F55" s="15" t="n">
+        <v>2700</v>
+      </c>
+      <c r="G55" s="15" t="n">
+        <v>2700</v>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>3115</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>6250</v>
+      </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -2653,10 +4827,49 @@
         <v>488</v>
       </c>
       <c r="M55" s="7" t="n"/>
-      <c r="N55" s="7" t="n"/>
-      <c r="O55" s="7" t="n"/>
+      <c r="N55" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-115 вып.2</t>
+        </is>
+      </c>
+      <c r="O55" s="16" t="inlineStr">
+        <is>
+          <t>Фундаменты под стальные опоры ВЛ 35–500 кВ (серия 3.407-115)</t>
+        </is>
+      </c>
       <c r="P55" s="7" t="n"/>
       <c r="Q55" s="7" t="n"/>
+      <c r="R55" s="16" t="inlineStr">
+        <is>
+          <t>B30</t>
+        </is>
+      </c>
+      <c r="S55" s="16" t="inlineStr">
+        <is>
+          <t>F300</t>
+        </is>
+      </c>
+      <c r="T55" s="16" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="U55" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V55" s="18" t="n">
+        <v>587</v>
+      </c>
+      <c r="W55" s="19" t="inlineStr">
+        <is>
+          <t>Ф5-Ам</t>
+        </is>
+      </c>
+      <c r="X55" s="21" t="inlineStr">
+        <is>
+          <t>Normadagi armatura 488 kg, seriyada jami po'lat 587 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -2696,6 +4909,17 @@
       <c r="O56" s="7" t="n"/>
       <c r="P56" s="7" t="n"/>
       <c r="Q56" s="7" t="n"/>
+      <c r="R56" s="20" t="n"/>
+      <c r="S56" s="20" t="n"/>
+      <c r="T56" s="20" t="n"/>
+      <c r="U56" s="20" t="n"/>
+      <c r="V56" s="20" t="n"/>
+      <c r="W56" s="20" t="n"/>
+      <c r="X56" s="22" t="inlineStr">
+        <is>
+          <t>zhbi5.ru da topilmadi — o'zingiz to'ldirasiz</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -2715,10 +4939,18 @@
       </c>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="8" t="n"/>
-      <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="n"/>
-      <c r="I57" s="8" t="n"/>
+      <c r="F57" s="23" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G57" s="23" t="n">
+        <v>2200</v>
+      </c>
+      <c r="H57" s="23" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I57" s="23" t="n">
+        <v>5100</v>
+      </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
           <t>М 400</t>
@@ -2730,11 +4962,46 @@
       <c r="L57" s="10" t="n">
         <v>699.7</v>
       </c>
-      <c r="M57" s="7" t="n"/>
-      <c r="N57" s="7" t="n"/>
-      <c r="O57" s="7" t="n"/>
+      <c r="M57" s="24" t="inlineStr">
+        <is>
+          <t>A-III (A400), A-I (A240)</t>
+        </is>
+      </c>
+      <c r="N57" s="24" t="inlineStr">
+        <is>
+          <t>Чертёж 70тм-25-1336а (АО САЭСП, 2007), на базе черт. 1141-25-46а</t>
+        </is>
+      </c>
+      <c r="O57" s="24" t="inlineStr">
+        <is>
+          <t>Фундамент с наклонной стойкой 250 мм под опору; анкерные болты М64</t>
+        </is>
+      </c>
       <c r="P57" s="7" t="n"/>
       <c r="Q57" s="7" t="n"/>
+      <c r="R57" s="24" t="inlineStr">
+        <is>
+          <t>B30</t>
+        </is>
+      </c>
+      <c r="S57" s="20" t="n"/>
+      <c r="T57" s="20" t="n"/>
+      <c r="U57" s="24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V57" s="24" t="n">
+        <v>878</v>
+      </c>
+      <c r="W57" s="24" t="inlineStr">
+        <is>
+          <t>chizma (IMG_0003.pdf)</t>
+        </is>
+      </c>
+      <c r="X57" s="24" t="inlineStr">
+        <is>
+          <t>Chizmadan to'ldirildi (yashil). F va W chizmada ko'rsatilmagan.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -2754,10 +5021,18 @@
       </c>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="8" t="n"/>
-      <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="n"/>
-      <c r="I58" s="8" t="n"/>
+      <c r="F58" s="15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G58" s="15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H58" s="15" t="n">
+        <v>1700</v>
+      </c>
+      <c r="I58" s="15" t="n">
+        <v>2500</v>
+      </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
           <t>М 300</t>
@@ -2770,10 +5045,49 @@
         <v>74.7</v>
       </c>
       <c r="M58" s="7" t="n"/>
-      <c r="N58" s="7" t="n"/>
-      <c r="O58" s="7" t="n"/>
+      <c r="N58" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-115 вып.3</t>
+        </is>
+      </c>
+      <c r="O58" s="16" t="inlineStr">
+        <is>
+          <t>Фундаменты под стальные опоры ВЛ 35–500 кВ (серия 3.407-115)</t>
+        </is>
+      </c>
       <c r="P58" s="7" t="n"/>
       <c r="Q58" s="7" t="n"/>
+      <c r="R58" s="16" t="inlineStr">
+        <is>
+          <t>B22,5</t>
+        </is>
+      </c>
+      <c r="S58" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T58" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U58" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V58" s="18" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="W58" s="19" t="inlineStr">
+        <is>
+          <t>ФК3-05</t>
+        </is>
+      </c>
+      <c r="X58" s="21" t="inlineStr">
+        <is>
+          <t>Normadagi hajm 1.17 ≠ seriyada 1.0 m³; Normadagi armatura 74.7 kg, seriyada jami po'lat 93.2 kg (zakladlar bilan) — farqni tekshiring</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -2793,10 +5107,18 @@
       </c>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="8" t="n"/>
-      <c r="G59" s="8" t="n"/>
-      <c r="H59" s="8" t="n"/>
-      <c r="I59" s="8" t="n"/>
+      <c r="F59" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G59" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H59" s="15" t="n">
+        <v>1700</v>
+      </c>
+      <c r="I59" s="15" t="n">
+        <v>2900</v>
+      </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
           <t>М 300</t>
@@ -2809,10 +5131,45 @@
         <v>127.7</v>
       </c>
       <c r="M59" s="7" t="n"/>
-      <c r="N59" s="7" t="n"/>
-      <c r="O59" s="7" t="n"/>
+      <c r="N59" s="16" t="inlineStr">
+        <is>
+          <t>Серия 3.407-115 вып.3</t>
+        </is>
+      </c>
+      <c r="O59" s="16" t="inlineStr">
+        <is>
+          <t>Фундаменты под стальные опоры ВЛ 35–500 кВ (серия 3.407-115)</t>
+        </is>
+      </c>
       <c r="P59" s="7" t="n"/>
       <c r="Q59" s="7" t="n"/>
+      <c r="R59" s="16" t="inlineStr">
+        <is>
+          <t>B22,5</t>
+        </is>
+      </c>
+      <c r="S59" s="16" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="T59" s="16" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="U59" s="17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V59" s="18" t="n">
+        <v>146</v>
+      </c>
+      <c r="W59" s="19" t="inlineStr">
+        <is>
+          <t>ФК4-05</t>
+        </is>
+      </c>
+      <c r="X59" s="20" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr"/>
@@ -2836,9 +5193,71 @@
       <c r="O60" s="7" t="n"/>
       <c r="P60" s="7" t="n"/>
       <c r="Q60" s="7" t="n"/>
+      <c r="R60" s="20" t="n"/>
+      <c r="S60" s="20" t="n"/>
+      <c r="T60" s="20" t="n"/>
+      <c r="U60" s="20" t="n"/>
+      <c r="V60" s="20" t="n"/>
+      <c r="W60" s="20" t="n"/>
+      <c r="X60" s="22" t="inlineStr">
+        <is>
+          <t>zhbi5.ru da aniq mos topilmadi (saytdagi «ПК-1» — подпятник, 0,15 t; buyurtmadagi narxi bilan to'g'ri kelmaydi) — o'zingiz to'ldirasiz</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Q60"/>
+  <autoFilter ref="A3:X60"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W28" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W29" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W30" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W31" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W32" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W33" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W34" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W35" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W36" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W37" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W38" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W39" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W40" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W41" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W42" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W43" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W44" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W45" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W46" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W47" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W49" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W50" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W51" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W53" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W54" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W55" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W58" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W59" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
